--- a/data/left_join.xlsx
+++ b/data/left_join.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -55,11 +58,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R277"/>
+  <dimension ref="A1:S277"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -517,6 +521,11 @@
       <c r="R1" s="1" t="inlineStr">
         <is>
           <t>cfaFr</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>date</t>
         </is>
       </c>
     </row>
@@ -563,6 +572,9 @@
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
+      <c r="S2" s="2" t="n">
+        <v>45992</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -607,6 +619,9 @@
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
+      <c r="S3" s="2" t="n">
+        <v>45962</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -651,6 +666,9 @@
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
+      <c r="S4" s="2" t="n">
+        <v>45931</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -695,6 +713,9 @@
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
+      <c r="S5" s="2" t="n">
+        <v>45901</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -739,6 +760,9 @@
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
+      <c r="S6" s="2" t="n">
+        <v>45870</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -783,6 +807,9 @@
       <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
+      <c r="S7" s="2" t="n">
+        <v>45839</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -827,6 +854,9 @@
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
+      <c r="S8" s="2" t="n">
+        <v>45809</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -871,6 +901,9 @@
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
+      <c r="S9" s="2" t="n">
+        <v>45778</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -915,6 +948,9 @@
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
+      <c r="S10" s="2" t="n">
+        <v>45748</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -959,6 +995,9 @@
       <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
+      <c r="S11" s="2" t="n">
+        <v>45717</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1003,6 +1042,9 @@
       <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
+      <c r="S12" s="2" t="n">
+        <v>45689</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1047,6 +1089,9 @@
       <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
+      <c r="S13" s="2" t="n">
+        <v>45658</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1091,6 +1136,9 @@
       <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
+      <c r="S14" s="2" t="n">
+        <v>45627</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1135,6 +1183,9 @@
       <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
+      <c r="S15" s="2" t="n">
+        <v>45597</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1179,6 +1230,9 @@
       <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
+      <c r="S16" s="2" t="n">
+        <v>45566</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1223,6 +1277,9 @@
       <c r="P17" t="inlineStr"/>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
+      <c r="S17" s="2" t="n">
+        <v>45536</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1267,6 +1324,9 @@
       <c r="P18" t="inlineStr"/>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
+      <c r="S18" s="2" t="n">
+        <v>45505</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1311,6 +1371,9 @@
       <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
+      <c r="S19" s="2" t="n">
+        <v>45474</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1355,6 +1418,9 @@
       <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
+      <c r="S20" s="2" t="n">
+        <v>45444</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1399,6 +1465,9 @@
       <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
+      <c r="S21" s="2" t="n">
+        <v>45413</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1443,6 +1512,9 @@
       <c r="P22" t="inlineStr"/>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr"/>
+      <c r="S22" s="2" t="n">
+        <v>45383</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1487,6 +1559,9 @@
       <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr"/>
+      <c r="S23" s="2" t="n">
+        <v>45352</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1531,6 +1606,9 @@
       <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr"/>
+      <c r="S24" s="2" t="n">
+        <v>45323</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1575,6 +1653,9 @@
       <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr"/>
+      <c r="S25" s="2" t="n">
+        <v>45292</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1619,6 +1700,9 @@
       <c r="P26" t="inlineStr"/>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr"/>
+      <c r="S26" s="2" t="n">
+        <v>45261</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1663,6 +1747,9 @@
       <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr"/>
+      <c r="S27" s="2" t="n">
+        <v>45231</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1707,6 +1794,9 @@
       <c r="P28" t="inlineStr"/>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr"/>
+      <c r="S28" s="2" t="n">
+        <v>45200</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1751,6 +1841,9 @@
       <c r="P29" t="inlineStr"/>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr"/>
+      <c r="S29" s="2" t="n">
+        <v>45170</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1795,6 +1888,9 @@
       <c r="P30" t="inlineStr"/>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr"/>
+      <c r="S30" s="2" t="n">
+        <v>45139</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1839,6 +1935,9 @@
       <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr"/>
+      <c r="S31" s="2" t="n">
+        <v>45108</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1883,6 +1982,9 @@
       <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr"/>
+      <c r="S32" s="2" t="n">
+        <v>45078</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1927,6 +2029,9 @@
       <c r="P33" t="inlineStr"/>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr"/>
+      <c r="S33" s="2" t="n">
+        <v>45047</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1971,6 +2076,9 @@
       <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr"/>
+      <c r="S34" s="2" t="n">
+        <v>45017</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -2015,6 +2123,9 @@
       <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr"/>
+      <c r="S35" s="2" t="n">
+        <v>44986</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -2059,6 +2170,9 @@
       <c r="P36" t="inlineStr"/>
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr"/>
+      <c r="S36" s="2" t="n">
+        <v>44958</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -2103,6 +2217,9 @@
       <c r="P37" t="inlineStr"/>
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr"/>
+      <c r="S37" s="2" t="n">
+        <v>44927</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -2147,6 +2264,9 @@
       <c r="P38" t="inlineStr"/>
       <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr"/>
+      <c r="S38" s="2" t="n">
+        <v>44896</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -2191,6 +2311,9 @@
       <c r="P39" t="inlineStr"/>
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr"/>
+      <c r="S39" s="2" t="n">
+        <v>44866</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -2235,6 +2358,9 @@
       <c r="P40" t="inlineStr"/>
       <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr"/>
+      <c r="S40" s="2" t="n">
+        <v>44835</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -2279,6 +2405,9 @@
       <c r="P41" t="inlineStr"/>
       <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr"/>
+      <c r="S41" s="2" t="n">
+        <v>44805</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -2323,6 +2452,9 @@
       <c r="P42" t="inlineStr"/>
       <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr"/>
+      <c r="S42" s="2" t="n">
+        <v>44774</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -2367,6 +2499,9 @@
       <c r="P43" t="inlineStr"/>
       <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr"/>
+      <c r="S43" s="2" t="n">
+        <v>44743</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -2411,6 +2546,9 @@
       <c r="P44" t="inlineStr"/>
       <c r="Q44" t="inlineStr"/>
       <c r="R44" t="inlineStr"/>
+      <c r="S44" s="2" t="n">
+        <v>44713</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -2455,6 +2593,9 @@
       <c r="P45" t="inlineStr"/>
       <c r="Q45" t="inlineStr"/>
       <c r="R45" t="inlineStr"/>
+      <c r="S45" s="2" t="n">
+        <v>44682</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -2499,6 +2640,9 @@
       <c r="P46" t="inlineStr"/>
       <c r="Q46" t="inlineStr"/>
       <c r="R46" t="inlineStr"/>
+      <c r="S46" s="2" t="n">
+        <v>44652</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -2543,6 +2687,9 @@
       <c r="P47" t="inlineStr"/>
       <c r="Q47" t="inlineStr"/>
       <c r="R47" t="inlineStr"/>
+      <c r="S47" s="2" t="n">
+        <v>44621</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -2587,6 +2734,9 @@
       <c r="P48" t="inlineStr"/>
       <c r="Q48" t="inlineStr"/>
       <c r="R48" t="inlineStr"/>
+      <c r="S48" s="2" t="n">
+        <v>44593</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -2631,6 +2781,9 @@
       <c r="P49" t="inlineStr"/>
       <c r="Q49" t="inlineStr"/>
       <c r="R49" t="inlineStr"/>
+      <c r="S49" s="2" t="n">
+        <v>44562</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -2675,6 +2828,9 @@
       <c r="P50" t="inlineStr"/>
       <c r="Q50" t="inlineStr"/>
       <c r="R50" t="inlineStr"/>
+      <c r="S50" s="2" t="n">
+        <v>44531</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -2719,6 +2875,9 @@
       <c r="P51" t="inlineStr"/>
       <c r="Q51" t="inlineStr"/>
       <c r="R51" t="inlineStr"/>
+      <c r="S51" s="2" t="n">
+        <v>44501</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -2763,6 +2922,9 @@
       <c r="P52" t="inlineStr"/>
       <c r="Q52" t="inlineStr"/>
       <c r="R52" t="inlineStr"/>
+      <c r="S52" s="2" t="n">
+        <v>44470</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -2807,6 +2969,9 @@
       <c r="P53" t="inlineStr"/>
       <c r="Q53" t="inlineStr"/>
       <c r="R53" t="inlineStr"/>
+      <c r="S53" s="2" t="n">
+        <v>44440</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -2851,6 +3016,9 @@
       <c r="P54" t="inlineStr"/>
       <c r="Q54" t="inlineStr"/>
       <c r="R54" t="inlineStr"/>
+      <c r="S54" s="2" t="n">
+        <v>44409</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -2895,6 +3063,9 @@
       <c r="P55" t="inlineStr"/>
       <c r="Q55" t="inlineStr"/>
       <c r="R55" t="inlineStr"/>
+      <c r="S55" s="2" t="n">
+        <v>44378</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -2939,6 +3110,9 @@
       <c r="P56" t="inlineStr"/>
       <c r="Q56" t="inlineStr"/>
       <c r="R56" t="inlineStr"/>
+      <c r="S56" s="2" t="n">
+        <v>44348</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -2983,6 +3157,9 @@
       <c r="P57" t="inlineStr"/>
       <c r="Q57" t="inlineStr"/>
       <c r="R57" t="inlineStr"/>
+      <c r="S57" s="2" t="n">
+        <v>44317</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -3047,6 +3224,9 @@
       <c r="R58" t="n">
         <v>0.6899999999999999</v>
       </c>
+      <c r="S58" s="2" t="n">
+        <v>44287</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -3111,6 +3291,9 @@
       <c r="R59" t="n">
         <v>0.6899999999999999</v>
       </c>
+      <c r="S59" s="2" t="n">
+        <v>44256</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -3175,6 +3358,9 @@
       <c r="R60" t="n">
         <v>0.7</v>
       </c>
+      <c r="S60" s="2" t="n">
+        <v>44228</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -3239,6 +3425,9 @@
       <c r="R61" t="n">
         <v>0.71</v>
       </c>
+      <c r="S61" s="2" t="n">
+        <v>44197</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -3303,6 +3492,9 @@
       <c r="R62" t="n">
         <v>0.7</v>
       </c>
+      <c r="S62" s="2" t="n">
+        <v>44166</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -3367,6 +3559,9 @@
       <c r="R63" t="n">
         <v>0.68</v>
       </c>
+      <c r="S63" s="2" t="n">
+        <v>44136</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -3431,6 +3626,9 @@
       <c r="R64" t="n">
         <v>0.68</v>
       </c>
+      <c r="S64" s="2" t="n">
+        <v>44105</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -3495,6 +3693,9 @@
       <c r="R65" t="n">
         <v>0.68</v>
       </c>
+      <c r="S65" s="2" t="n">
+        <v>44075</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -3559,6 +3760,9 @@
       <c r="R66" t="n">
         <v>0.66</v>
       </c>
+      <c r="S66" s="2" t="n">
+        <v>44044</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -3623,6 +3827,9 @@
       <c r="R67" t="n">
         <v>0.53</v>
       </c>
+      <c r="S67" s="2" t="n">
+        <v>44013</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -3687,6 +3894,9 @@
       <c r="R68" t="n">
         <v>0.53</v>
       </c>
+      <c r="S68" s="2" t="n">
+        <v>43983</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -3751,6 +3961,9 @@
       <c r="R69" t="n">
         <v>0.51</v>
       </c>
+      <c r="S69" s="2" t="n">
+        <v>43952</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -3815,6 +4028,9 @@
       <c r="R70" t="n">
         <v>0.51</v>
       </c>
+      <c r="S70" s="2" t="n">
+        <v>43922</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -3879,6 +4095,9 @@
       <c r="R71" t="n">
         <v>0.52</v>
       </c>
+      <c r="S71" s="2" t="n">
+        <v>43891</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -3943,6 +4162,9 @@
       <c r="R72" t="n">
         <v>0.5</v>
       </c>
+      <c r="S72" s="2" t="n">
+        <v>43862</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -4007,6 +4229,9 @@
       <c r="R73" t="n">
         <v>0.52</v>
       </c>
+      <c r="S73" s="2" t="n">
+        <v>43831</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -4071,6 +4296,9 @@
       <c r="R74" t="n">
         <v>0.52</v>
       </c>
+      <c r="S74" s="2" t="n">
+        <v>43800</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -4135,6 +4363,9 @@
       <c r="R75" t="n">
         <v>0.52</v>
       </c>
+      <c r="S75" s="2" t="n">
+        <v>43770</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -4199,6 +4430,9 @@
       <c r="R76" t="n">
         <v>0.52</v>
       </c>
+      <c r="S76" s="2" t="n">
+        <v>43739</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -4263,6 +4497,9 @@
       <c r="R77" t="n">
         <v>0.51</v>
       </c>
+      <c r="S77" s="2" t="n">
+        <v>43709</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -4327,6 +4564,9 @@
       <c r="R78" t="n">
         <v>0.52</v>
       </c>
+      <c r="S78" s="2" t="n">
+        <v>43678</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -4391,6 +4631,9 @@
       <c r="R79" t="n">
         <v>0.53</v>
       </c>
+      <c r="S79" s="2" t="n">
+        <v>43647</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -4455,6 +4698,9 @@
       <c r="R80" t="n">
         <v>0.53</v>
       </c>
+      <c r="S80" s="2" t="n">
+        <v>43617</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -4519,6 +4765,9 @@
       <c r="R81" t="n">
         <v>0.52</v>
       </c>
+      <c r="S81" s="2" t="n">
+        <v>43586</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -4583,6 +4832,9 @@
       <c r="R82" t="n">
         <v>0.53</v>
       </c>
+      <c r="S82" s="2" t="n">
+        <v>43556</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -4647,6 +4899,9 @@
       <c r="R83" t="n">
         <v>0.53</v>
       </c>
+      <c r="S83" s="2" t="n">
+        <v>43525</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -4711,6 +4966,9 @@
       <c r="R84" t="n">
         <v>0.53</v>
       </c>
+      <c r="S84" s="2" t="n">
+        <v>43497</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -4775,6 +5033,9 @@
       <c r="R85" t="n">
         <v>0.53</v>
       </c>
+      <c r="S85" s="2" t="n">
+        <v>43466</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -4839,6 +5100,9 @@
       <c r="R86" t="n">
         <v>0.53</v>
       </c>
+      <c r="S86" s="2" t="n">
+        <v>43435</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -4903,6 +5167,9 @@
       <c r="R87" t="n">
         <v>0.53</v>
       </c>
+      <c r="S87" s="2" t="n">
+        <v>43405</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -4967,6 +5234,9 @@
       <c r="R88" t="n">
         <v>0.54</v>
       </c>
+      <c r="S88" s="2" t="n">
+        <v>43374</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -5031,6 +5301,9 @@
       <c r="R89" t="n">
         <v>0.54</v>
       </c>
+      <c r="S89" s="2" t="n">
+        <v>43344</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -5095,6 +5368,9 @@
       <c r="R90" t="n">
         <v>0.54</v>
       </c>
+      <c r="S90" s="2" t="n">
+        <v>43313</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -5159,6 +5435,9 @@
       <c r="R91" t="n">
         <v>0.54</v>
       </c>
+      <c r="S91" s="2" t="n">
+        <v>43282</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -5223,6 +5502,9 @@
       <c r="R92" t="n">
         <v>0.54</v>
       </c>
+      <c r="S92" s="2" t="n">
+        <v>43252</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -5287,6 +5569,9 @@
       <c r="R93" t="n">
         <v>0.55</v>
       </c>
+      <c r="S93" s="2" t="n">
+        <v>43221</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -5351,6 +5636,9 @@
       <c r="R94" t="n">
         <v>0.57</v>
       </c>
+      <c r="S94" s="2" t="n">
+        <v>43191</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -5415,6 +5703,9 @@
       <c r="R95" t="n">
         <v>0.57</v>
       </c>
+      <c r="S95" s="2" t="n">
+        <v>43160</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -5479,6 +5770,9 @@
       <c r="R96" t="n">
         <v>0.58</v>
       </c>
+      <c r="S96" s="2" t="n">
+        <v>43132</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -5543,6 +5837,9 @@
       <c r="R97" t="n">
         <v>0.57</v>
       </c>
+      <c r="S97" s="2" t="n">
+        <v>43101</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -5607,6 +5904,9 @@
       <c r="R98" t="n">
         <v>0.55</v>
       </c>
+      <c r="S98" s="2" t="n">
+        <v>43070</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -5671,6 +5971,9 @@
       <c r="R99" t="n">
         <v>0.54</v>
       </c>
+      <c r="S99" s="2" t="n">
+        <v>43040</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -5735,6 +6038,9 @@
       <c r="R100" t="n">
         <v>0.55</v>
       </c>
+      <c r="S100" s="2" t="n">
+        <v>43009</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -5799,6 +6105,9 @@
       <c r="R101" t="n">
         <v>0.5600000000000001</v>
       </c>
+      <c r="S101" s="2" t="n">
+        <v>42979</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -5863,6 +6172,9 @@
       <c r="R102" t="n">
         <v>0.55</v>
       </c>
+      <c r="S102" s="2" t="n">
+        <v>42948</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -5927,6 +6239,9 @@
       <c r="R103" t="n">
         <v>0.54</v>
       </c>
+      <c r="S103" s="2" t="n">
+        <v>42917</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -5991,6 +6306,9 @@
       <c r="R104" t="n">
         <v>0.52</v>
       </c>
+      <c r="S104" s="2" t="n">
+        <v>42887</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -6055,6 +6373,9 @@
       <c r="R105" t="n">
         <v>0.51</v>
       </c>
+      <c r="S105" s="2" t="n">
+        <v>42856</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -6119,6 +6440,9 @@
       <c r="R106" t="n">
         <v>0.5</v>
       </c>
+      <c r="S106" s="2" t="n">
+        <v>42826</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -6183,6 +6507,9 @@
       <c r="R107" t="n">
         <v>0.5</v>
       </c>
+      <c r="S107" s="2" t="n">
+        <v>42795</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -6247,6 +6574,9 @@
       <c r="R108" t="n">
         <v>0.5</v>
       </c>
+      <c r="S108" s="2" t="n">
+        <v>42767</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -6311,6 +6641,9 @@
       <c r="R109" t="n">
         <v>0.49</v>
       </c>
+      <c r="S109" s="2" t="n">
+        <v>42736</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -6375,6 +6708,9 @@
       <c r="R110" t="n">
         <v>0.47</v>
       </c>
+      <c r="S110" s="2" t="n">
+        <v>42705</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -6439,6 +6775,9 @@
       <c r="R111" t="n">
         <v>0.5</v>
       </c>
+      <c r="S111" s="2" t="n">
+        <v>42675</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -6503,6 +6842,9 @@
       <c r="R112" t="n">
         <v>0.51</v>
       </c>
+      <c r="S112" s="2" t="n">
+        <v>42644</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -6567,6 +6909,9 @@
       <c r="R113" t="n">
         <v>0.52</v>
       </c>
+      <c r="S113" s="2" t="n">
+        <v>42614</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -6631,6 +6976,9 @@
       <c r="R114" t="n">
         <v>0.53</v>
       </c>
+      <c r="S114" s="2" t="n">
+        <v>42583</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -6695,6 +7043,9 @@
       <c r="R115" t="n">
         <v>0.49</v>
       </c>
+      <c r="S115" s="2" t="n">
+        <v>42552</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -6759,6 +7110,9 @@
       <c r="R116" t="n">
         <v>0.38</v>
       </c>
+      <c r="S116" s="2" t="n">
+        <v>42522</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -6823,6 +7177,9 @@
       <c r="R117" t="n">
         <v>0.34</v>
       </c>
+      <c r="S117" s="2" t="n">
+        <v>42491</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -6887,6 +7244,9 @@
       <c r="R118" t="n">
         <v>0.34</v>
       </c>
+      <c r="S118" s="2" t="n">
+        <v>42461</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -6951,6 +7311,9 @@
       <c r="R119" t="n">
         <v>0.33</v>
       </c>
+      <c r="S119" s="2" t="n">
+        <v>42430</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -7015,6 +7378,9 @@
       <c r="R120" t="n">
         <v>0.33</v>
       </c>
+      <c r="S120" s="2" t="n">
+        <v>42401</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -7079,6 +7445,9 @@
       <c r="R121" t="n">
         <v>0.33</v>
       </c>
+      <c r="S121" s="2" t="n">
+        <v>42370</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -7143,6 +7512,9 @@
       <c r="R122" t="n">
         <v>0.32</v>
       </c>
+      <c r="S122" s="2" t="n">
+        <v>42339</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -7207,6 +7579,9 @@
       <c r="R123" t="n">
         <v>0.32</v>
       </c>
+      <c r="S123" s="2" t="n">
+        <v>42309</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -7271,6 +7646,9 @@
       <c r="R124" t="n">
         <v>0.34</v>
       </c>
+      <c r="S124" s="2" t="n">
+        <v>42278</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -7335,6 +7713,9 @@
       <c r="R125" t="n">
         <v>0.34</v>
       </c>
+      <c r="S125" s="2" t="n">
+        <v>42248</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -7399,6 +7780,9 @@
       <c r="R126" t="n">
         <v>0.33</v>
       </c>
+      <c r="S126" s="2" t="n">
+        <v>42217</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -7463,6 +7847,9 @@
       <c r="R127" t="n">
         <v>0.33</v>
       </c>
+      <c r="S127" s="2" t="n">
+        <v>42186</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -7527,6 +7914,9 @@
       <c r="R128" t="n">
         <v>0.34</v>
       </c>
+      <c r="S128" s="2" t="n">
+        <v>42156</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -7591,6 +7981,9 @@
       <c r="R129" t="n">
         <v>0.34</v>
       </c>
+      <c r="S129" s="2" t="n">
+        <v>42125</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -7655,6 +8048,9 @@
       <c r="R130" t="n">
         <v>0.32</v>
       </c>
+      <c r="S130" s="2" t="n">
+        <v>42095</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -7719,6 +8115,9 @@
       <c r="R131" t="n">
         <v>0.32</v>
       </c>
+      <c r="S131" s="2" t="n">
+        <v>42064</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -7783,6 +8182,9 @@
       <c r="R132" t="n">
         <v>0.31</v>
       </c>
+      <c r="S132" s="2" t="n">
+        <v>42036</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -7847,6 +8249,9 @@
       <c r="R133" t="n">
         <v>0.3</v>
       </c>
+      <c r="S133" s="2" t="n">
+        <v>42005</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -7911,6 +8316,9 @@
       <c r="R134" t="n">
         <v>0.32</v>
       </c>
+      <c r="S134" s="2" t="n">
+        <v>41974</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -7975,6 +8383,9 @@
       <c r="R135" t="n">
         <v>0.3</v>
       </c>
+      <c r="S135" s="2" t="n">
+        <v>41944</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -8039,6 +8450,9 @@
       <c r="R136" t="n">
         <v>0.3</v>
       </c>
+      <c r="S136" s="2" t="n">
+        <v>41913</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -8103,6 +8517,9 @@
       <c r="R137" t="n">
         <v>0.31</v>
       </c>
+      <c r="S137" s="2" t="n">
+        <v>41883</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -8167,6 +8584,9 @@
       <c r="R138" t="n">
         <v>0.32</v>
       </c>
+      <c r="S138" s="2" t="n">
+        <v>41852</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -8231,6 +8651,9 @@
       <c r="R139" t="n">
         <v>0.32</v>
       </c>
+      <c r="S139" s="2" t="n">
+        <v>41821</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -8295,6 +8718,9 @@
       <c r="R140" t="n">
         <v>0.32</v>
       </c>
+      <c r="S140" s="2" t="n">
+        <v>41791</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -8359,6 +8785,9 @@
       <c r="R141" t="n">
         <v>0.33</v>
       </c>
+      <c r="S141" s="2" t="n">
+        <v>41760</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -8423,6 +8852,9 @@
       <c r="R142" t="n">
         <v>0.33</v>
       </c>
+      <c r="S142" s="2" t="n">
+        <v>41730</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -8487,6 +8919,9 @@
       <c r="R143" t="n">
         <v>0.33</v>
       </c>
+      <c r="S143" s="2" t="n">
+        <v>41699</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -8551,6 +8986,9 @@
       <c r="R144" t="n">
         <v>0.32</v>
       </c>
+      <c r="S144" s="2" t="n">
+        <v>41671</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -8615,6 +9053,9 @@
       <c r="R145" t="n">
         <v>0.32</v>
       </c>
+      <c r="S145" s="2" t="n">
+        <v>41640</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -8679,6 +9120,9 @@
       <c r="R146" t="n">
         <v>0.32</v>
       </c>
+      <c r="S146" s="2" t="n">
+        <v>41609</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -8743,6 +9187,9 @@
       <c r="R147" t="n">
         <v>0.32</v>
       </c>
+      <c r="S147" s="2" t="n">
+        <v>41579</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -8807,6 +9254,9 @@
       <c r="R148" t="n">
         <v>0.32</v>
       </c>
+      <c r="S148" s="2" t="n">
+        <v>41548</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -8871,6 +9321,9 @@
       <c r="R149" t="n">
         <v>0.32</v>
       </c>
+      <c r="S149" s="2" t="n">
+        <v>41518</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -8935,6 +9388,9 @@
       <c r="R150" t="n">
         <v>0.31</v>
       </c>
+      <c r="S150" s="2" t="n">
+        <v>41487</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -8999,6 +9455,9 @@
       <c r="R151" t="n">
         <v>0.3</v>
       </c>
+      <c r="S151" s="2" t="n">
+        <v>41456</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -9063,6 +9522,9 @@
       <c r="R152" t="n">
         <v>0.31</v>
       </c>
+      <c r="S152" s="2" t="n">
+        <v>41426</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -9127,6 +9589,9 @@
       <c r="R153" t="n">
         <v>0.31</v>
       </c>
+      <c r="S153" s="2" t="n">
+        <v>41395</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -9191,6 +9656,9 @@
       <c r="R154" t="n">
         <v>0.31</v>
       </c>
+      <c r="S154" s="2" t="n">
+        <v>41365</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -9255,6 +9723,9 @@
       <c r="R155" t="n">
         <v>0.31</v>
       </c>
+      <c r="S155" s="2" t="n">
+        <v>41334</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -9319,6 +9790,9 @@
       <c r="R156" t="n">
         <v>0.32</v>
       </c>
+      <c r="S156" s="2" t="n">
+        <v>41306</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -9383,6 +9857,9 @@
       <c r="R157" t="n">
         <v>0.31</v>
       </c>
+      <c r="S157" s="2" t="n">
+        <v>41275</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -9447,6 +9924,9 @@
       <c r="R158" t="n">
         <v>0.31</v>
       </c>
+      <c r="S158" s="2" t="n">
+        <v>41244</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -9511,6 +9991,9 @@
       <c r="R159" t="n">
         <v>0.3</v>
       </c>
+      <c r="S159" s="2" t="n">
+        <v>41214</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -9575,6 +10058,9 @@
       <c r="R160" t="n">
         <v>0.31</v>
       </c>
+      <c r="S160" s="2" t="n">
+        <v>41183</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -9639,6 +10125,9 @@
       <c r="R161" t="n">
         <v>0.3</v>
       </c>
+      <c r="S161" s="2" t="n">
+        <v>41153</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -9703,6 +10192,9 @@
       <c r="R162" t="n">
         <v>0.29</v>
       </c>
+      <c r="S162" s="2" t="n">
+        <v>41122</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -9767,6 +10259,9 @@
       <c r="R163" t="n">
         <v>0.29</v>
       </c>
+      <c r="S163" s="2" t="n">
+        <v>41091</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -9831,6 +10326,9 @@
       <c r="R164" t="n">
         <v>0.3</v>
       </c>
+      <c r="S164" s="2" t="n">
+        <v>41061</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -9895,6 +10393,9 @@
       <c r="R165" t="n">
         <v>0.3</v>
       </c>
+      <c r="S165" s="2" t="n">
+        <v>41030</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -9959,6 +10460,9 @@
       <c r="R166" t="n">
         <v>0.31</v>
       </c>
+      <c r="S166" s="2" t="n">
+        <v>41000</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -10023,6 +10527,9 @@
       <c r="R167" t="n">
         <v>0.31</v>
       </c>
+      <c r="S167" s="2" t="n">
+        <v>40969</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -10087,6 +10594,9 @@
       <c r="R168" t="n">
         <v>0.31</v>
       </c>
+      <c r="S168" s="2" t="n">
+        <v>40940</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -10151,6 +10661,9 @@
       <c r="R169" t="n">
         <v>0.31</v>
       </c>
+      <c r="S169" s="2" t="n">
+        <v>40909</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -10215,6 +10728,9 @@
       <c r="R170" t="n">
         <v>0.31</v>
       </c>
+      <c r="S170" s="2" t="n">
+        <v>40878</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -10279,6 +10795,9 @@
       <c r="R171" t="n">
         <v>0.32</v>
       </c>
+      <c r="S171" s="2" t="n">
+        <v>40848</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -10343,6 +10862,9 @@
       <c r="R172" t="n">
         <v>0.32</v>
       </c>
+      <c r="S172" s="2" t="n">
+        <v>40817</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -10407,6 +10929,9 @@
       <c r="R173" t="n">
         <v>0.32</v>
       </c>
+      <c r="S173" s="2" t="n">
+        <v>40787</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -10471,6 +10996,9 @@
       <c r="R174" t="n">
         <v>0.33</v>
       </c>
+      <c r="S174" s="2" t="n">
+        <v>40756</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -10535,6 +11063,9 @@
       <c r="R175" t="n">
         <v>0.33</v>
       </c>
+      <c r="S175" s="2" t="n">
+        <v>40725</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -10599,6 +11130,9 @@
       <c r="R176" t="n">
         <v>0.34</v>
       </c>
+      <c r="S176" s="2" t="n">
+        <v>40695</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -10663,6 +11197,9 @@
       <c r="R177" t="n">
         <v>0.33</v>
       </c>
+      <c r="S177" s="2" t="n">
+        <v>40664</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -10727,6 +11264,9 @@
       <c r="R178" t="n">
         <v>0.33</v>
       </c>
+      <c r="S178" s="2" t="n">
+        <v>40634</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -10791,6 +11331,9 @@
       <c r="R179" t="n">
         <v>0.32</v>
       </c>
+      <c r="S179" s="2" t="n">
+        <v>40603</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -10855,6 +11398,9 @@
       <c r="R180" t="n">
         <v>0.31</v>
       </c>
+      <c r="S180" s="2" t="n">
+        <v>40575</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -10919,6 +11465,9 @@
       <c r="R181" t="n">
         <v>0.3</v>
       </c>
+      <c r="S181" s="2" t="n">
+        <v>40544</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -10983,6 +11532,9 @@
       <c r="R182" t="n">
         <v>0.3</v>
       </c>
+      <c r="S182" s="2" t="n">
+        <v>40513</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -11047,6 +11599,9 @@
       <c r="R183" t="n">
         <v>0.31</v>
       </c>
+      <c r="S183" s="2" t="n">
+        <v>40483</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -11111,6 +11666,9 @@
       <c r="R184" t="n">
         <v>0.32</v>
       </c>
+      <c r="S184" s="2" t="n">
+        <v>40452</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -11175,6 +11733,9 @@
       <c r="R185" t="n">
         <v>0.3</v>
       </c>
+      <c r="S185" s="2" t="n">
+        <v>40422</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -11239,6 +11800,9 @@
       <c r="R186" t="n">
         <v>0.29</v>
       </c>
+      <c r="S186" s="2" t="n">
+        <v>40391</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -11303,6 +11867,9 @@
       <c r="R187" t="n">
         <v>0.29</v>
       </c>
+      <c r="S187" s="2" t="n">
+        <v>40360</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -11367,6 +11934,9 @@
       <c r="R188" t="n">
         <v>0.28</v>
       </c>
+      <c r="S188" s="2" t="n">
+        <v>40330</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -11431,6 +12001,9 @@
       <c r="R189" t="n">
         <v>0.28</v>
       </c>
+      <c r="S189" s="2" t="n">
+        <v>40299</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -11495,6 +12068,9 @@
       <c r="R190" t="n">
         <v>0.28</v>
       </c>
+      <c r="S190" s="2" t="n">
+        <v>40269</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -11559,6 +12135,9 @@
       <c r="R191" t="n">
         <v>0.31</v>
       </c>
+      <c r="S191" s="2" t="n">
+        <v>40238</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -11623,6 +12202,9 @@
       <c r="R192" t="n">
         <v>0.31</v>
       </c>
+      <c r="S192" s="2" t="n">
+        <v>40210</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -11687,6 +12269,9 @@
       <c r="R193" t="n">
         <v>0.32</v>
       </c>
+      <c r="S193" s="2" t="n">
+        <v>40179</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -11751,6 +12336,9 @@
       <c r="R194" t="n">
         <v>0.33</v>
       </c>
+      <c r="S194" s="2" t="n">
+        <v>40148</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -11815,6 +12403,9 @@
       <c r="R195" t="n">
         <v>0.34</v>
       </c>
+      <c r="S195" s="2" t="n">
+        <v>40118</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -11879,6 +12470,9 @@
       <c r="R196" t="n">
         <v>0.33</v>
       </c>
+      <c r="S196" s="2" t="n">
+        <v>40087</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -11943,6 +12537,9 @@
       <c r="R197" t="n">
         <v>0.33</v>
       </c>
+      <c r="S197" s="2" t="n">
+        <v>40057</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -12007,6 +12604,9 @@
       <c r="R198" t="n">
         <v>0.36</v>
       </c>
+      <c r="S198" s="2" t="n">
+        <v>40026</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -12071,6 +12671,9 @@
       <c r="R199" t="n">
         <v>0.32</v>
       </c>
+      <c r="S199" s="2" t="n">
+        <v>39995</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -12135,6 +12738,9 @@
       <c r="R200" t="n">
         <v>0.31</v>
       </c>
+      <c r="S200" s="2" t="n">
+        <v>39965</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -12199,6 +12805,9 @@
       <c r="R201" t="n">
         <v>0.3</v>
       </c>
+      <c r="S201" s="2" t="n">
+        <v>39934</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -12263,6 +12872,9 @@
       <c r="R202" t="n">
         <v>0.29</v>
       </c>
+      <c r="S202" s="2" t="n">
+        <v>39904</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -12327,6 +12939,9 @@
       <c r="R203" t="n">
         <v>0.29</v>
       </c>
+      <c r="S203" s="2" t="n">
+        <v>39873</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -12391,6 +13006,9 @@
       <c r="R204" t="n">
         <v>0.28</v>
       </c>
+      <c r="S204" s="2" t="n">
+        <v>39845</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -12455,6 +13073,9 @@
       <c r="R205" t="n">
         <v>0.29</v>
       </c>
+      <c r="S205" s="2" t="n">
+        <v>39814</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -12519,6 +13140,9 @@
       <c r="R206" t="n">
         <v>0.26</v>
       </c>
+      <c r="S206" s="2" t="n">
+        <v>39783</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -12583,6 +13207,9 @@
       <c r="R207" t="n">
         <v>0.23</v>
       </c>
+      <c r="S207" s="2" t="n">
+        <v>39753</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -12647,6 +13274,9 @@
       <c r="R208" t="n">
         <v>0.24</v>
       </c>
+      <c r="S208" s="2" t="n">
+        <v>39722</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -12711,6 +13341,9 @@
       <c r="R209" t="n">
         <v>0.26</v>
       </c>
+      <c r="S209" s="2" t="n">
+        <v>39692</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -12775,6 +13408,9 @@
       <c r="R210" t="n">
         <v>0.27</v>
       </c>
+      <c r="S210" s="2" t="n">
+        <v>39661</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -12839,6 +13475,9 @@
       <c r="R211" t="n">
         <v>0.28</v>
       </c>
+      <c r="S211" s="2" t="n">
+        <v>39630</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -12903,6 +13542,9 @@
       <c r="R212" t="n">
         <v>0.27</v>
       </c>
+      <c r="S212" s="2" t="n">
+        <v>39600</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -12967,6 +13609,9 @@
       <c r="R213" t="n">
         <v>0.28</v>
       </c>
+      <c r="S213" s="2" t="n">
+        <v>39569</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -13031,6 +13676,9 @@
       <c r="R214" t="n">
         <v>0.28</v>
       </c>
+      <c r="S214" s="2" t="n">
+        <v>39539</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -13095,6 +13743,9 @@
       <c r="R215" t="n">
         <v>0.27</v>
       </c>
+      <c r="S215" s="2" t="n">
+        <v>39508</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -13159,6 +13810,9 @@
       <c r="R216" t="n">
         <v>0.26</v>
       </c>
+      <c r="S216" s="2" t="n">
+        <v>39479</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -13223,6 +13877,9 @@
       <c r="R217" t="n">
         <v>0.26</v>
       </c>
+      <c r="S217" s="2" t="n">
+        <v>39448</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -13287,6 +13944,9 @@
       <c r="R218" t="n">
         <v>0.26</v>
       </c>
+      <c r="S218" s="2" t="n">
+        <v>39417</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -13351,6 +14011,9 @@
       <c r="R219" t="n">
         <v>0.26</v>
       </c>
+      <c r="S219" s="2" t="n">
+        <v>39387</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -13415,6 +14078,9 @@
       <c r="R220" t="n">
         <v>0.27</v>
       </c>
+      <c r="S220" s="2" t="n">
+        <v>39356</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -13479,6 +14145,9 @@
       <c r="R221" t="n">
         <v>0.26</v>
       </c>
+      <c r="S221" s="2" t="n">
+        <v>39326</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -13543,6 +14212,9 @@
       <c r="R222" t="n">
         <v>0.26</v>
       </c>
+      <c r="S222" s="2" t="n">
+        <v>39295</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -13607,6 +14279,9 @@
       <c r="R223" t="n">
         <v>0.26</v>
       </c>
+      <c r="S223" s="2" t="n">
+        <v>39264</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -13671,6 +14346,9 @@
       <c r="R224" t="n">
         <v>0.26</v>
       </c>
+      <c r="S224" s="2" t="n">
+        <v>39234</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -13735,6 +14413,9 @@
       <c r="R225" t="n">
         <v>0.25</v>
       </c>
+      <c r="S225" s="2" t="n">
+        <v>39203</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -13799,6 +14480,9 @@
       <c r="R226" t="n">
         <v>0.26</v>
       </c>
+      <c r="S226" s="2" t="n">
+        <v>39173</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -13863,6 +14547,9 @@
       <c r="R227" t="n">
         <v>0.25</v>
       </c>
+      <c r="S227" s="2" t="n">
+        <v>39142</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -13927,6 +14614,9 @@
       <c r="R228" t="n">
         <v>0.24</v>
       </c>
+      <c r="S228" s="2" t="n">
+        <v>39114</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -13991,6 +14681,9 @@
       <c r="R229" t="n">
         <v>0.25</v>
       </c>
+      <c r="S229" s="2" t="n">
+        <v>39083</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -14055,6 +14748,9 @@
       <c r="R230" t="n">
         <v>0.24</v>
       </c>
+      <c r="S230" s="2" t="n">
+        <v>39052</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -14119,6 +14815,9 @@
       <c r="R231" t="n">
         <v>0.25</v>
       </c>
+      <c r="S231" s="2" t="n">
+        <v>39022</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -14183,6 +14882,9 @@
       <c r="R232" t="n">
         <v>0.25</v>
       </c>
+      <c r="S232" s="2" t="n">
+        <v>38991</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -14247,6 +14949,9 @@
       <c r="R233" t="n">
         <v>0.25</v>
       </c>
+      <c r="S233" s="2" t="n">
+        <v>38961</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -14311,6 +15016,9 @@
       <c r="R234" t="n">
         <v>0.25</v>
       </c>
+      <c r="S234" s="2" t="n">
+        <v>38930</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -14375,6 +15083,9 @@
       <c r="R235" t="n">
         <v>0.24</v>
       </c>
+      <c r="S235" s="2" t="n">
+        <v>38899</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -14439,6 +15150,9 @@
       <c r="R236" t="n">
         <v>0.24</v>
       </c>
+      <c r="S236" s="2" t="n">
+        <v>38869</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -14503,6 +15217,9 @@
       <c r="R237" t="n">
         <v>0.25</v>
       </c>
+      <c r="S237" s="2" t="n">
+        <v>38838</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -14567,6 +15284,9 @@
       <c r="R238" t="n">
         <v>0.24</v>
       </c>
+      <c r="S238" s="2" t="n">
+        <v>38808</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -14631,6 +15351,9 @@
       <c r="R239" t="n">
         <v>0.23</v>
       </c>
+      <c r="S239" s="2" t="n">
+        <v>38777</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -14695,6 +15418,9 @@
       <c r="R240" t="n">
         <v>0.23</v>
       </c>
+      <c r="S240" s="2" t="n">
+        <v>38749</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -14759,6 +15485,9 @@
       <c r="R241" t="n">
         <v>0.24</v>
       </c>
+      <c r="S241" s="2" t="n">
+        <v>38718</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -14823,6 +15552,9 @@
       <c r="R242" t="n">
         <v>0.23</v>
       </c>
+      <c r="S242" s="2" t="n">
+        <v>38687</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -14887,6 +15619,9 @@
       <c r="R243" t="n">
         <v>0.23</v>
       </c>
+      <c r="S243" s="2" t="n">
+        <v>38657</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -14951,6 +15686,9 @@
       <c r="R244" t="n">
         <v>0.24</v>
       </c>
+      <c r="S244" s="2" t="n">
+        <v>38626</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -15015,6 +15753,9 @@
       <c r="R245" t="n">
         <v>0.24</v>
       </c>
+      <c r="S245" s="2" t="n">
+        <v>38596</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -15079,6 +15820,9 @@
       <c r="R246" t="n">
         <v>0.25</v>
       </c>
+      <c r="S246" s="2" t="n">
+        <v>38565</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -15143,6 +15887,9 @@
       <c r="R247" t="n">
         <v>0.24</v>
       </c>
+      <c r="S247" s="2" t="n">
+        <v>38534</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -15207,6 +15954,9 @@
       <c r="R248" t="n">
         <v>0.25</v>
       </c>
+      <c r="S248" s="2" t="n">
+        <v>38504</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -15271,6 +16021,9 @@
       <c r="R249" t="n">
         <v>0.26</v>
       </c>
+      <c r="S249" s="2" t="n">
+        <v>38473</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -15335,6 +16088,9 @@
       <c r="R250" t="n">
         <v>0.26</v>
       </c>
+      <c r="S250" s="2" t="n">
+        <v>38443</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -15399,6 +16155,9 @@
       <c r="R251" t="n">
         <v>0.27</v>
       </c>
+      <c r="S251" s="2" t="n">
+        <v>38412</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -15463,6 +16222,9 @@
       <c r="R252" t="n">
         <v>0.26</v>
       </c>
+      <c r="S252" s="2" t="n">
+        <v>38384</v>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -15527,6 +16289,9 @@
       <c r="R253" t="n">
         <v>0.27</v>
       </c>
+      <c r="S253" s="2" t="n">
+        <v>38353</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -15591,6 +16356,9 @@
       <c r="R254" t="n">
         <v>0.27</v>
       </c>
+      <c r="S254" s="2" t="n">
+        <v>38322</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -15655,6 +16423,9 @@
       <c r="R255" t="n">
         <v>0.26</v>
       </c>
+      <c r="S255" s="2" t="n">
+        <v>38292</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -15719,6 +16490,9 @@
       <c r="R256" t="n">
         <v>0.25</v>
       </c>
+      <c r="S256" s="2" t="n">
+        <v>38261</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -15783,6 +16557,9 @@
       <c r="R257" t="n">
         <v>0.25</v>
       </c>
+      <c r="S257" s="2" t="n">
+        <v>38231</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -15847,6 +16624,9 @@
       <c r="R258" t="n">
         <v>0.25</v>
       </c>
+      <c r="S258" s="2" t="n">
+        <v>38200</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -15911,6 +16691,9 @@
       <c r="R259" t="n">
         <v>0.25</v>
       </c>
+      <c r="S259" s="2" t="n">
+        <v>38169</v>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
@@ -15975,6 +16758,9 @@
       <c r="R260" t="n">
         <v>0.24</v>
       </c>
+      <c r="S260" s="2" t="n">
+        <v>38139</v>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -16039,6 +16825,9 @@
       <c r="R261" t="n">
         <v>0.24</v>
       </c>
+      <c r="S261" s="2" t="n">
+        <v>38108</v>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -16103,6 +16892,9 @@
       <c r="R262" t="n">
         <v>0.24</v>
       </c>
+      <c r="S262" s="2" t="n">
+        <v>38078</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -16167,6 +16959,9 @@
       <c r="R263" t="n">
         <v>0.25</v>
       </c>
+      <c r="S263" s="2" t="n">
+        <v>38047</v>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
@@ -16231,6 +17026,9 @@
       <c r="R264" t="n">
         <v>0.2</v>
       </c>
+      <c r="S264" s="2" t="n">
+        <v>38018</v>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
@@ -16294,6 +17092,9 @@
       </c>
       <c r="R265" t="n">
         <v>0.16</v>
+      </c>
+      <c r="S265" s="2" t="n">
+        <v>37987</v>
       </c>
     </row>
     <row r="266">
@@ -16339,6 +17140,9 @@
       <c r="P266" t="inlineStr"/>
       <c r="Q266" t="inlineStr"/>
       <c r="R266" t="inlineStr"/>
+      <c r="S266" s="2" t="n">
+        <v>37956</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
@@ -16383,6 +17187,9 @@
       <c r="P267" t="inlineStr"/>
       <c r="Q267" t="inlineStr"/>
       <c r="R267" t="inlineStr"/>
+      <c r="S267" s="2" t="n">
+        <v>37926</v>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
@@ -16427,6 +17234,9 @@
       <c r="P268" t="inlineStr"/>
       <c r="Q268" t="inlineStr"/>
       <c r="R268" t="inlineStr"/>
+      <c r="S268" s="2" t="n">
+        <v>37895</v>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
@@ -16471,6 +17281,9 @@
       <c r="P269" t="inlineStr"/>
       <c r="Q269" t="inlineStr"/>
       <c r="R269" t="inlineStr"/>
+      <c r="S269" s="2" t="n">
+        <v>37865</v>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
@@ -16515,6 +17328,9 @@
       <c r="P270" t="inlineStr"/>
       <c r="Q270" t="inlineStr"/>
       <c r="R270" t="inlineStr"/>
+      <c r="S270" s="2" t="n">
+        <v>37834</v>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
@@ -16559,6 +17375,9 @@
       <c r="P271" t="inlineStr"/>
       <c r="Q271" t="inlineStr"/>
       <c r="R271" t="inlineStr"/>
+      <c r="S271" s="2" t="n">
+        <v>37803</v>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
@@ -16603,6 +17422,9 @@
       <c r="P272" t="inlineStr"/>
       <c r="Q272" t="inlineStr"/>
       <c r="R272" t="inlineStr"/>
+      <c r="S272" s="2" t="n">
+        <v>37773</v>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
@@ -16647,6 +17469,9 @@
       <c r="P273" t="inlineStr"/>
       <c r="Q273" t="inlineStr"/>
       <c r="R273" t="inlineStr"/>
+      <c r="S273" s="2" t="n">
+        <v>37742</v>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
@@ -16691,6 +17516,9 @@
       <c r="P274" t="inlineStr"/>
       <c r="Q274" t="inlineStr"/>
       <c r="R274" t="inlineStr"/>
+      <c r="S274" s="2" t="n">
+        <v>37712</v>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
@@ -16735,6 +17563,9 @@
       <c r="P275" t="inlineStr"/>
       <c r="Q275" t="inlineStr"/>
       <c r="R275" t="inlineStr"/>
+      <c r="S275" s="2" t="n">
+        <v>37681</v>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
@@ -16779,6 +17610,9 @@
       <c r="P276" t="inlineStr"/>
       <c r="Q276" t="inlineStr"/>
       <c r="R276" t="inlineStr"/>
+      <c r="S276" s="2" t="n">
+        <v>37653</v>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
@@ -16823,6 +17657,9 @@
       <c r="P277" t="inlineStr"/>
       <c r="Q277" t="inlineStr"/>
       <c r="R277" t="inlineStr"/>
+      <c r="S277" s="2" t="n">
+        <v>37622</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
